--- a/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
@@ -8,38 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC336233-69C6-440E-8EF9-DD15D32861B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883A62F6-0F79-4C7F-9A62-7DBD1E7424BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | AUGUST" sheetId="902" r:id="rId1"/>
     <sheet name="(01)" sheetId="1847" r:id="rId2"/>
-    <sheet name="08-01 R1" sheetId="1848" r:id="rId3"/>
-    <sheet name="08-01 R2" sheetId="1849" r:id="rId4"/>
-    <sheet name="08-01 R3" sheetId="1850" r:id="rId5"/>
+    <sheet name="08-01 R1 NO TRIP" sheetId="1848" r:id="rId3"/>
+    <sheet name="08-01 R2 NO TRIP" sheetId="1849" r:id="rId4"/>
+    <sheet name="08-01 R3 NO TRIP" sheetId="1850" r:id="rId5"/>
     <sheet name="(3)" sheetId="1855" r:id="rId6"/>
     <sheet name="08-03 R1" sheetId="1856" r:id="rId7"/>
     <sheet name="08-03 R2" sheetId="1857" r:id="rId8"/>
     <sheet name="08-03 R3" sheetId="1858" r:id="rId9"/>
     <sheet name="(4)" sheetId="1859" r:id="rId10"/>
-    <sheet name="08-04 R1" sheetId="1860" r:id="rId11"/>
+    <sheet name="08-04 R1 NO TRIP" sheetId="1860" r:id="rId11"/>
     <sheet name="08-04 R2" sheetId="1861" r:id="rId12"/>
     <sheet name="08-04 R3" sheetId="1862" r:id="rId13"/>
+    <sheet name="(5)" sheetId="1863" r:id="rId14"/>
+    <sheet name="08-04 R1 (2)" sheetId="1864" r:id="rId15"/>
+    <sheet name="08-04 R2 (2)" sheetId="1865" r:id="rId16"/>
+    <sheet name="08-04 R3 (2)" sheetId="1866" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'(01)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'(3)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'(4)'!$A$1:$Z$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'08-01 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'08-01 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'08-01 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'(5)'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'08-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'08-01 R2 NO TRIP'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'08-01 R3 NO TRIP'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'08-03 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'08-03 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'08-03 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'08-04 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'08-04 R1 (2)'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'08-04 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'08-04 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'08-04 R2 (2)'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08-04 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'08-04 R3 (2)'!$A$1:$V$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="87">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -276,6 +284,48 @@
   </si>
   <si>
     <t>DATE ___________08/04/2026___________</t>
+  </si>
+  <si>
+    <t>17/3B</t>
+  </si>
+  <si>
+    <t>5/5B</t>
+  </si>
+  <si>
+    <t>22/8B</t>
+  </si>
+  <si>
+    <t>10/3B</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>25/8B</t>
+  </si>
+  <si>
+    <t>26/8B</t>
+  </si>
+  <si>
+    <t>2/8B</t>
+  </si>
+  <si>
+    <t>10/8B</t>
+  </si>
+  <si>
+    <t>17/5B</t>
+  </si>
+  <si>
+    <t>20/5B</t>
+  </si>
+  <si>
+    <t>11/4B</t>
+  </si>
+  <si>
+    <t>1/20B</t>
   </si>
 </sst>
 </file>
@@ -896,7 +946,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1148,6 +1198,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,6 +1236,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2708,47 +2765,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -2980,12 +3037,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4239,47 +4296,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -4511,12 +4568,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4552,17 +4609,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4922,12 +4979,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>78</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -4940,9 +5003,13 @@
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
+      <c r="U8" s="14">
+        <v>1</v>
+      </c>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -5110,12 +5177,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>2</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -5128,9 +5201,13 @@
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
+      <c r="U15" s="23">
+        <v>1</v>
+      </c>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -5138,12 +5215,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>85</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -5156,9 +5239,13 @@
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
+      <c r="U16" s="28">
+        <v>0</v>
+      </c>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -5521,20 +5608,34 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="78"/>
+      <c r="F24" s="94">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>12</v>
+      </c>
+      <c r="M24" s="14">
+        <v>514</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>16</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -5707,20 +5808,34 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>1</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>10</v>
+      </c>
+      <c r="M31" s="23">
+        <v>83</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>16</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -5735,20 +5850,34 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>0</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>20</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>431</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -5786,47 +5915,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5888,18 +6017,30 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>466</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
       <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="P36" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>5</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -6046,24 +6187,36 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>466</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
       <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="P42" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>5</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6099,17 +6252,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>11+20+2+431</f>
+        <v>464</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6469,12 +6628,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>84</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -6486,12 +6651,18 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
       <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -6657,12 +6828,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>3</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -6674,23 +6851,35 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>83</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -6702,12 +6891,18 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>2</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>4</v>
+      </c>
       <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -7073,21 +7268,31 @@
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>56</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>27</v>
+      </c>
+      <c r="M24" s="14">
+        <v>652</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -7259,21 +7464,31 @@
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>23</v>
+      </c>
+      <c r="M31" s="23">
+        <v>104</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>1</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -7287,21 +7502,31 @@
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>55</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>4</v>
+      </c>
+      <c r="M32" s="28">
+        <v>548</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>0</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -7333,47 +7558,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -7435,18 +7660,38 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>620</v>
+      </c>
+      <c r="G36" s="42">
+        <v>2</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>6</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="L36" s="42">
+        <v>5</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>14</v>
+      </c>
+      <c r="O36" s="42">
+        <v>9</v>
+      </c>
+      <c r="P36" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>2</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -7593,24 +7838,44 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>620</v>
+      </c>
+      <c r="G42" s="42">
+        <v>2</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>6</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="L42" s="42">
+        <v>5</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>14</v>
+      </c>
+      <c r="O42" s="42">
+        <v>9</v>
+      </c>
+      <c r="P42" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>2</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -7646,17 +7911,6192 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>17+2+4+55+4+548</f>
+        <v>630</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806A6571-CF25-4678-B6D0-4645912075C5}">
+  <dimension ref="B1:AA43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="88"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="81"/>
+      <c r="W35" s="81"/>
+      <c r="X35" s="81"/>
+      <c r="Y35" s="81"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="81"/>
+      <c r="V36" s="81"/>
+      <c r="W36" s="81"/>
+      <c r="X36" s="81"/>
+      <c r="Y36" s="81"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="81"/>
+      <c r="V37" s="81"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
+      <c r="Y37" s="81"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="81"/>
+      <c r="V38" s="81"/>
+      <c r="W38" s="81"/>
+      <c r="X38" s="81"/>
+      <c r="Y38" s="81"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="81"/>
+      <c r="W39" s="81"/>
+      <c r="X39" s="81"/>
+      <c r="Y39" s="81"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="81"/>
+      <c r="V40" s="81"/>
+      <c r="W40" s="81"/>
+      <c r="X40" s="81"/>
+      <c r="Y40" s="81"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="81"/>
+      <c r="W41" s="81"/>
+      <c r="X41" s="81"/>
+      <c r="Y41" s="81"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="81"/>
+      <c r="V43" s="81"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="81"/>
+      <c r="Y43" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A15E81-9B9D-499E-BD02-1FF77BF73DC7}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="88"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="81"/>
+      <c r="W35" s="81"/>
+      <c r="X35" s="81"/>
+      <c r="Y35" s="81"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="81"/>
+      <c r="V36" s="81"/>
+      <c r="W36" s="81"/>
+      <c r="X36" s="81"/>
+      <c r="Y36" s="81"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="81"/>
+      <c r="V37" s="81"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
+      <c r="Y37" s="81"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="81"/>
+      <c r="V38" s="81"/>
+      <c r="W38" s="81"/>
+      <c r="X38" s="81"/>
+      <c r="Y38" s="81"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="81"/>
+      <c r="W39" s="81"/>
+      <c r="X39" s="81"/>
+      <c r="Y39" s="81"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="81"/>
+      <c r="V40" s="81"/>
+      <c r="W40" s="81"/>
+      <c r="X40" s="81"/>
+      <c r="Y40" s="81"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="81"/>
+      <c r="W41" s="81"/>
+      <c r="X41" s="81"/>
+      <c r="Y41" s="81"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="81"/>
+      <c r="V43" s="81"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="81"/>
+      <c r="Y43" s="81"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09538259-9426-4E87-8477-6ED5679A0012}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="88"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="81"/>
+      <c r="W35" s="81"/>
+      <c r="X35" s="81"/>
+      <c r="Y35" s="81"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="81"/>
+      <c r="V36" s="81"/>
+      <c r="W36" s="81"/>
+      <c r="X36" s="81"/>
+      <c r="Y36" s="81"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="81"/>
+      <c r="V37" s="81"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
+      <c r="Y37" s="81"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="81"/>
+      <c r="V38" s="81"/>
+      <c r="W38" s="81"/>
+      <c r="X38" s="81"/>
+      <c r="Y38" s="81"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="81"/>
+      <c r="W39" s="81"/>
+      <c r="X39" s="81"/>
+      <c r="Y39" s="81"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="81"/>
+      <c r="V40" s="81"/>
+      <c r="W40" s="81"/>
+      <c r="X40" s="81"/>
+      <c r="Y40" s="81"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="81"/>
+      <c r="W41" s="81"/>
+      <c r="X41" s="81"/>
+      <c r="Y41" s="81"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="81"/>
+      <c r="V43" s="81"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="81"/>
+      <c r="Y43" s="81"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF346F00-3A13-4DF3-90F2-F4B30087CD4C}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="88"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="81"/>
+      <c r="W35" s="81"/>
+      <c r="X35" s="81"/>
+      <c r="Y35" s="81"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="81"/>
+      <c r="V36" s="81"/>
+      <c r="W36" s="81"/>
+      <c r="X36" s="81"/>
+      <c r="Y36" s="81"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="81"/>
+      <c r="V37" s="81"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
+      <c r="Y37" s="81"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="81"/>
+      <c r="V38" s="81"/>
+      <c r="W38" s="81"/>
+      <c r="X38" s="81"/>
+      <c r="Y38" s="81"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="81"/>
+      <c r="W39" s="81"/>
+      <c r="X39" s="81"/>
+      <c r="Y39" s="81"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="81"/>
+      <c r="V40" s="81"/>
+      <c r="W40" s="81"/>
+      <c r="X40" s="81"/>
+      <c r="Y40" s="81"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="81"/>
+      <c r="W41" s="81"/>
+      <c r="X41" s="81"/>
+      <c r="Y41" s="81"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="81"/>
+      <c r="V43" s="81"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="81"/>
+      <c r="Y43" s="81"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8877,47 +15317,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -9149,12 +15589,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -10408,47 +16848,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -10680,12 +17120,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -10721,17 +17161,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -11955,47 +18395,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -12227,12 +18667,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -12268,17 +18708,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13502,47 +19942,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13774,12 +20214,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13815,17 +20255,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -15046,47 +21486,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15318,12 +21758,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15714,11 +22154,15 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -15730,10 +22174,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -15902,11 +22350,15 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>8</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -15918,10 +22370,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -15930,11 +22386,15 @@
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="D16" s="58">
+        <v>1</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>81</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -15946,10 +22406,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -16317,15 +22781,25 @@
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>32</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>369</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>9</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -16503,15 +22977,25 @@
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>86</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>9</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -16531,15 +23015,25 @@
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>32</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>9</v>
+      </c>
+      <c r="M32" s="28">
+        <v>283</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -16577,47 +23071,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16679,18 +23173,40 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>309</v>
+      </c>
+      <c r="G36" s="42">
+        <v>4</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="I36" s="42">
+        <v>11</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>5</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>16</v>
+      </c>
+      <c r="O36" s="42">
+        <v>1</v>
+      </c>
+      <c r="P36" s="42">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>13</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -16837,24 +23353,46 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>309</v>
+      </c>
+      <c r="G42" s="42">
+        <v>4</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="I42" s="42">
+        <v>11</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>5</v>
+      </c>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>16</v>
+      </c>
+      <c r="O42" s="42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="42">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>13</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -16890,17 +23428,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>1+2+1+32+9+283</f>
+        <v>328</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -17260,12 +23804,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -17278,9 +23832,13 @@
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
+      <c r="U8" s="14">
+        <v>1</v>
+      </c>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -17448,12 +24006,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>2</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -17466,9 +24034,13 @@
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
+      <c r="U15" s="23">
+        <v>0</v>
+      </c>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -17476,12 +24048,22 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>79</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -17494,9 +24076,13 @@
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
+      <c r="U16" s="28">
+        <v>1</v>
+      </c>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -17859,20 +24445,36 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>3</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="78"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="H24" s="14">
+        <v>168</v>
+      </c>
+      <c r="I24" s="14">
+        <v>1</v>
+      </c>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="L24" s="14">
+        <v>9</v>
+      </c>
+      <c r="M24" s="14">
+        <v>615</v>
+      </c>
+      <c r="N24" s="14">
+        <v>2</v>
+      </c>
+      <c r="O24" s="14">
+        <v>1</v>
+      </c>
+      <c r="P24" s="14">
+        <v>16</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -18045,20 +24647,36 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>1</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
+      <c r="I31" s="23">
+        <v>0</v>
+      </c>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="L31" s="23">
+        <v>3</v>
+      </c>
+      <c r="M31" s="23">
+        <v>128</v>
+      </c>
+      <c r="N31" s="23">
+        <v>0</v>
+      </c>
+      <c r="O31" s="23">
+        <v>0</v>
+      </c>
+      <c r="P31" s="23">
+        <v>16</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -18073,20 +24691,36 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>2</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="H32" s="28">
+        <v>168</v>
+      </c>
+      <c r="I32" s="28">
+        <v>1</v>
+      </c>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="L32" s="28">
+        <v>6</v>
+      </c>
+      <c r="M32" s="28">
+        <v>487</v>
+      </c>
+      <c r="N32" s="28">
+        <v>2</v>
+      </c>
+      <c r="O32" s="23">
+        <v>1</v>
+      </c>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -18124,47 +24758,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18223,21 +24857,41 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>3</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>664</v>
+      </c>
+      <c r="G36" s="42">
+        <v>3</v>
+      </c>
+      <c r="H36" s="42">
+        <v>10</v>
+      </c>
+      <c r="I36" s="42">
+        <v>2</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>10</v>
+      </c>
+      <c r="L36" s="42">
+        <v>7</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>8</v>
+      </c>
+      <c r="P36" s="42">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>4</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -18381,27 +25035,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>664</v>
+      </c>
+      <c r="G42" s="42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="42">
+        <v>10</v>
+      </c>
+      <c r="I42" s="42">
+        <v>2</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>10</v>
+      </c>
+      <c r="L42" s="42">
+        <v>7</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="O42" s="42">
+        <v>8</v>
+      </c>
+      <c r="P42" s="42">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>4</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18437,17 +25111,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>1+1+25+1+2+168+1+6+487+2+1</f>
+        <v>695</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -18807,12 +25487,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>75</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -18827,9 +25513,15 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -18995,12 +25687,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>74</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -19015,20 +25713,32 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>73</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -19043,9 +25753,15 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>2</v>
+      </c>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -19409,23 +26125,35 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>90</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>540</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -19595,23 +26323,35 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>9</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>6</v>
+      </c>
+      <c r="M31" s="23">
+        <v>112</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>1</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -19623,23 +26363,35 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>81</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>14</v>
+      </c>
+      <c r="M32" s="28">
+        <v>428</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>0</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -19671,47 +26423,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -19773,18 +26525,38 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>572</v>
+      </c>
+      <c r="G36" s="42">
+        <v>4</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>16</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>3</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
       <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="N36" s="42">
+        <v>5</v>
+      </c>
+      <c r="O36" s="42">
+        <v>6</v>
+      </c>
+      <c r="P36" s="42">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>15</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -19931,24 +26703,44 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>572</v>
+      </c>
+      <c r="G42" s="42">
+        <v>4</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>16</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>3</v>
+      </c>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
       <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="N42" s="42">
+        <v>5</v>
+      </c>
+      <c r="O42" s="42">
+        <v>6</v>
+      </c>
+      <c r="P42" s="42">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>15</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -19984,17 +26776,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>17+2+1+2+81+14+428</f>
+        <v>545</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <f>3</f>
+        <v>3</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B052C-31CF-4EF8-84ED-50F82723D379}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2D16E9-3AA3-48EC-963E-AA75FD268CCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="14" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="18" activeTab="19" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | AUGUST" sheetId="902" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <sheet name="08-05 R2" sheetId="1865" r:id="rId16"/>
     <sheet name="08-05 R3 NO TRIP" sheetId="1866" r:id="rId17"/>
     <sheet name="(6)" sheetId="1867" r:id="rId18"/>
-    <sheet name="08-06 R1" sheetId="1868" r:id="rId19"/>
+    <sheet name="08-06 R1 NO TRIP" sheetId="1868" r:id="rId19"/>
     <sheet name="08-06 R2" sheetId="1869" r:id="rId20"/>
     <sheet name="08-06 R3" sheetId="1870" r:id="rId21"/>
     <sheet name="(7)" sheetId="1871" r:id="rId22"/>
@@ -68,7 +68,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08-05 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08-05 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'08-05 R3 NO TRIP'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'08-06 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'08-06 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'08-06 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'08-06 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'08-07 R1'!$A$1:$Z$43</definedName>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="101">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -382,6 +382,24 @@
   </si>
   <si>
     <t>10/10B</t>
+  </si>
+  <si>
+    <t>11/5B</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>11/10B</t>
+  </si>
+  <si>
+    <t>1/12B</t>
+  </si>
+  <si>
+    <t>11/12B</t>
+  </si>
+  <si>
+    <t>5/3B</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1020,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1263,6 +1281,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2824,47 +2845,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3096,12 +3117,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4355,47 +4376,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -4627,12 +4648,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4668,17 +4689,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5974,47 +5995,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6270,12 +6291,12 @@
       <c r="Q42" s="43">
         <v>5</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6311,23 +6332,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>11+20+2+431</f>
         <v>464</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7617,47 +7638,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -7929,12 +7950,12 @@
       <c r="Q42" s="43">
         <v>2</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -7970,23 +7991,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>17+2+4+55+4+548</f>
         <v>630</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <f>5</f>
         <v>5</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9207,47 +9228,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -9479,12 +9500,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -10792,47 +10813,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11108,12 +11129,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11149,20 +11170,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>8+113+15+236</f>
         <v>372</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12476,47 +12497,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -12792,12 +12813,12 @@
         <v>6</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -12833,22 +12854,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>2+10+1+1+1+21+1+322+1</f>
         <v>360</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>10</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14072,47 +14093,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -14344,12 +14365,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -14385,17 +14406,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -15616,47 +15637,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15888,12 +15909,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17147,47 +17168,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -17419,12 +17440,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17460,17 +17481,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -18691,47 +18712,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18963,12 +18984,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -19356,12 +19377,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -19376,7 +19403,9 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -19544,12 +19573,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>98</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -19564,7 +19599,9 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -19572,12 +19609,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -19592,7 +19635,9 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -19958,23 +20003,37 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="78"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>29</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>69</v>
+      </c>
+      <c r="L24" s="14">
+        <v>12</v>
+      </c>
+      <c r="M24" s="14">
+        <v>428</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -20144,23 +20203,37 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>43</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>100</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>1</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -20172,23 +20245,37 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>3</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>28</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>67</v>
+      </c>
+      <c r="L32" s="28">
+        <v>12</v>
+      </c>
+      <c r="M32" s="28">
+        <v>385</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>0</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -20220,47 +20307,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -20310,38 +20397,50 @@
       <c r="S35" s="70"/>
       <c r="T35" s="70"/>
       <c r="U35" s="71"/>
-      <c r="V35" s="82"/>
-      <c r="W35" s="82"/>
-      <c r="X35" s="82"/>
-      <c r="Y35" s="82"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
     </row>
     <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>3</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>457</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>4</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>67</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="O36" s="42">
+        <v>11</v>
+      </c>
+      <c r="P36" s="42">
+        <v>6</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
-      <c r="U36" s="82"/>
-      <c r="V36" s="82"/>
-      <c r="W36" s="82"/>
-      <c r="X36" s="82"/>
-      <c r="Y36" s="82"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
     </row>
     <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="53"/>
@@ -20363,11 +20462,11 @@
       <c r="R37" s="72"/>
       <c r="S37" s="44"/>
       <c r="T37" s="44"/>
-      <c r="U37" s="82"/>
-      <c r="V37" s="82"/>
-      <c r="W37" s="82"/>
-      <c r="X37" s="82"/>
-      <c r="Y37" s="82"/>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="84"/>
     </row>
     <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="53"/>
@@ -20389,11 +20488,11 @@
       <c r="R38" s="72"/>
       <c r="S38" s="44"/>
       <c r="T38" s="44"/>
-      <c r="U38" s="82"/>
-      <c r="V38" s="82"/>
-      <c r="W38" s="82"/>
-      <c r="X38" s="82"/>
-      <c r="Y38" s="82"/>
+      <c r="U38" s="84"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="84"/>
+      <c r="Y38" s="84"/>
     </row>
     <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="53"/>
@@ -20415,11 +20514,11 @@
       <c r="R39" s="72"/>
       <c r="S39" s="44"/>
       <c r="T39" s="44"/>
-      <c r="U39" s="82"/>
-      <c r="V39" s="82"/>
-      <c r="W39" s="82"/>
-      <c r="X39" s="82"/>
-      <c r="Y39" s="82"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
     </row>
     <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="53"/>
@@ -20441,11 +20540,11 @@
       <c r="R40" s="72"/>
       <c r="S40" s="44"/>
       <c r="T40" s="44"/>
-      <c r="U40" s="82"/>
-      <c r="V40" s="82"/>
-      <c r="W40" s="82"/>
-      <c r="X40" s="82"/>
-      <c r="Y40" s="82"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
     </row>
     <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="54"/>
@@ -20468,36 +20567,48 @@
       <c r="S41" s="74"/>
       <c r="T41" s="74"/>
       <c r="U41" s="75"/>
-      <c r="V41" s="82"/>
-      <c r="W41" s="82"/>
-      <c r="X41" s="82"/>
-      <c r="Y41" s="82"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
     </row>
     <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>457</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>4</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>67</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="O42" s="42">
+        <v>11</v>
+      </c>
+      <c r="P42" s="42">
+        <v>6</v>
+      </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -20533,17 +20644,21 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96">
+        <v>506</v>
+      </c>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96">
+        <v>12</v>
+      </c>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -20903,12 +21018,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>78</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -20923,7 +21044,9 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -21091,12 +21214,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>96</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -21111,7 +21240,9 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -21119,12 +21250,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>95</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -21139,7 +21276,9 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -21505,17 +21644,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>3</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>20</v>
+      </c>
+      <c r="L24" s="14">
+        <v>12</v>
+      </c>
+      <c r="M24" s="14">
+        <v>455</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>16</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -21691,17 +21842,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>3</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>88</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>16</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -21719,17 +21882,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>3</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>0</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>20</v>
+      </c>
+      <c r="L32" s="28">
+        <v>12</v>
+      </c>
+      <c r="M32" s="28">
+        <v>367</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -21767,47 +21942,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21866,21 +22041,43 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>5</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>378</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>9</v>
+      </c>
+      <c r="L36" s="42">
+        <v>13</v>
+      </c>
+      <c r="M36" s="42">
+        <v>7</v>
+      </c>
+      <c r="N36" s="42">
+        <v>2</v>
+      </c>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
+      <c r="P36" s="42">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>8</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -22024,27 +22221,49 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>5</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>378</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>9</v>
+      </c>
+      <c r="L42" s="42">
+        <v>13</v>
+      </c>
+      <c r="M42" s="42">
+        <v>7</v>
+      </c>
+      <c r="N42" s="42">
+        <v>2</v>
+      </c>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
+      <c r="P42" s="42">
+        <v>6</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>8</v>
+      </c>
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -22080,17 +22299,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96">
+        <f>1+11+1+3+20+12+367</f>
+        <v>415</v>
+      </c>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96">
+        <v>5</v>
+      </c>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23311,47 +23535,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23583,12 +23807,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -24842,47 +25066,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -25114,12 +25338,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -25155,17 +25379,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -26389,47 +26613,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26661,12 +26885,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26702,17 +26926,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -27936,47 +28160,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -28208,12 +28432,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28249,17 +28473,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -29480,47 +29704,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -29752,12 +29976,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -31011,47 +31235,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -31283,12 +31507,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -31324,17 +31548,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -32558,47 +32782,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -32830,12 +33054,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -32871,17 +33095,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -34105,47 +34329,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -34377,12 +34601,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -34418,17 +34642,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35654,47 +35878,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -35926,12 +36150,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -35967,17 +36191,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -37198,47 +37422,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -37470,12 +37694,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -38729,47 +38953,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -39001,12 +39225,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -39042,17 +39266,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -40276,47 +40500,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -40548,12 +40772,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -40589,17 +40813,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -41823,47 +42047,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -42095,12 +42319,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -42136,17 +42360,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -43370,47 +43594,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -43642,12 +43866,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -43683,17 +43907,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -44917,47 +45141,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -45189,12 +45413,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -45230,17 +45454,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -46461,47 +46685,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -46733,12 +46957,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -48046,47 +48270,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -48362,12 +48586,12 @@
       <c r="Q42" s="43">
         <v>13</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -48403,23 +48627,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>1+2+1+32+9+283</f>
         <v>328</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <f>8</f>
         <v>8</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -49733,47 +49957,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -50045,12 +50269,12 @@
       <c r="Q42" s="43">
         <v>4</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -50086,23 +50310,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>1+1+25+1+2+168+1+6+487+2+1</f>
         <v>695</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <f>8</f>
         <v>8</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -51398,47 +51622,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -51710,12 +51934,12 @@
       <c r="Q42" s="43">
         <v>15</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -51751,23 +51975,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>17+2+1+2+81+14+428</f>
         <v>545</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <f>3</f>
         <v>3</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2D16E9-3AA3-48EC-963E-AA75FD268CCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F109269C-A65A-4BED-A361-D0745636C771}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="18" activeTab="19" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="18" activeTab="22" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | AUGUST" sheetId="902" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="107">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -400,6 +400,24 @@
   </si>
   <si>
     <t>5/3B</t>
+  </si>
+  <si>
+    <t>14/4B</t>
+  </si>
+  <si>
+    <t>16/12B</t>
+  </si>
+  <si>
+    <t>3/17B</t>
+  </si>
+  <si>
+    <t>4/7B</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10/5B</t>
   </si>
 </sst>
 </file>
@@ -24203,11 +24221,15 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>8</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -24219,10 +24241,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -24391,11 +24417,15 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -24407,10 +24437,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -24419,11 +24453,15 @@
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>103</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -24435,10 +24473,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -24804,17 +24846,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>45</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>15</v>
+      </c>
+      <c r="M24" s="14">
+        <v>602</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>9</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -24990,17 +25044,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>8</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>120</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>9</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -25018,17 +25084,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>37</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>15</v>
+      </c>
+      <c r="M32" s="28">
+        <v>482</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -25165,21 +25243,37 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>2</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>528</v>
+      </c>
       <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
+      <c r="I36" s="42">
+        <v>7</v>
+      </c>
+      <c r="J36" s="42">
+        <v>2</v>
+      </c>
+      <c r="K36" s="42">
+        <v>15</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>15</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -25323,21 +25417,37 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>2</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>528</v>
+      </c>
       <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
+      <c r="I42" s="42">
+        <v>7</v>
+      </c>
+      <c r="J42" s="42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="42">
+        <v>15</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>15</v>
+      </c>
       <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
@@ -25379,7 +25489,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="96"/>
+      <c r="C44" s="96">
+        <f>3+2+37+15+482</f>
+        <v>539</v>
+      </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96"/>
     </row>
@@ -25387,7 +25500,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="96"/>
+      <c r="C45" s="96">
+        <v>17</v>
+      </c>
       <c r="D45" s="96"/>
       <c r="E45" s="96"/>
     </row>
@@ -25749,12 +25864,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -25766,12 +25887,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -25937,12 +26066,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>98</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -25954,23 +26089,37 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>106</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -25982,12 +26131,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -26351,17 +26508,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="78"/>
+      <c r="F24" s="83">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>24</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>12</v>
+      </c>
+      <c r="M24" s="14">
+        <v>416</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>16</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -26537,17 +26706,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>43</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>16</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -26565,17 +26746,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>24</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>12</v>
+      </c>
+      <c r="M32" s="28">
+        <v>373</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -26713,20 +26906,40 @@
         <v>52</v>
       </c>
       <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="42">
+        <v>21</v>
+      </c>
+      <c r="F36" s="42">
+        <v>448</v>
+      </c>
+      <c r="G36" s="42">
+        <v>7</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>9</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="42">
+        <v>7</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
+      <c r="P36" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>8</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -26871,20 +27084,40 @@
         <v>53</v>
       </c>
       <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
+      <c r="E42" s="42">
+        <v>21</v>
+      </c>
+      <c r="F42" s="42">
+        <v>448</v>
+      </c>
+      <c r="G42" s="42">
+        <v>7</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="42">
+        <v>7</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
+      <c r="P42" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>8</v>
+      </c>
       <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
@@ -26926,7 +27159,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="96"/>
+      <c r="C44" s="96">
+        <f>10+1+24+12+373</f>
+        <v>420</v>
+      </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96"/>
     </row>
@@ -26934,7 +27170,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="96"/>
+      <c r="C45" s="96">
+        <v>5</v>
+      </c>
       <c r="D45" s="96"/>
       <c r="E45" s="96"/>
     </row>
@@ -27296,12 +27534,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>102</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -27313,12 +27561,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>6</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -27484,12 +27740,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -27501,23 +27767,41 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>6</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>101</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -27529,12 +27813,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -27898,23 +28190,37 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>109</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>4</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>475</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -28084,23 +28390,37 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>3</v>
+      </c>
+      <c r="L31" s="23">
+        <v>16</v>
+      </c>
+      <c r="M31" s="23">
+        <v>88</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>100</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>1</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -28112,23 +28432,37 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>108</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>4</v>
+      </c>
+      <c r="M32" s="28">
+        <v>387</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>0</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -28262,18 +28596,32 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>481</v>
+      </c>
+      <c r="G36" s="42">
+        <v>10</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="I36" s="42">
+        <v>21</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>5</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>14</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>4</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -28420,18 +28768,32 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>481</v>
+      </c>
+      <c r="G42" s="42">
+        <v>10</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="I42" s="42">
+        <v>21</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>5</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>14</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>4</v>
+      </c>
       <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
@@ -28473,7 +28835,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="96"/>
+      <c r="C44" s="96">
+        <f>1+1+14+108+1+4+387</f>
+        <v>516</v>
+      </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96"/>
     </row>
@@ -28481,7 +28846,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="96"/>
+      <c r="C45" s="96">
+        <v>4</v>
+      </c>
       <c r="D45" s="96"/>
       <c r="E45" s="96"/>
     </row>

--- a/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/CSR MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F109269C-A65A-4BED-A361-D0745636C771}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9482DD-3346-4CC6-B7D5-64FB1E924B64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="18" activeTab="22" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="18" activeTab="27" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | AUGUST" sheetId="902" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <sheet name="08-07 R2" sheetId="1873" r:id="rId24"/>
     <sheet name="08-07 R3" sheetId="1874" r:id="rId25"/>
     <sheet name="(8)" sheetId="1875" r:id="rId26"/>
-    <sheet name="08-08 R1" sheetId="1876" r:id="rId27"/>
+    <sheet name="08-08 R1 NO TRIP" sheetId="1876" r:id="rId27"/>
     <sheet name="08-08 R2" sheetId="1877" r:id="rId28"/>
     <sheet name="08-08 R3" sheetId="1878" r:id="rId29"/>
     <sheet name="(10)" sheetId="1879" r:id="rId30"/>
@@ -74,7 +74,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="22">'08-07 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'08-07 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="24">'08-07 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="26">'08-08 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'08-08 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="27">'08-08 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'08-08 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="30">'08-10 R1'!$A$1:$Z$43</definedName>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="110">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -418,6 +418,15 @@
   </si>
   <si>
     <t>10/5B</t>
+  </si>
+  <si>
+    <t>7/1B</t>
+  </si>
+  <si>
+    <t>5/7B</t>
+  </si>
+  <si>
+    <t>12/8B</t>
   </si>
 </sst>
 </file>
@@ -32285,12 +32294,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>12</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -32302,12 +32317,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -32473,12 +32496,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>98</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -32490,23 +32519,37 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>11</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -32518,12 +32561,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -32887,17 +32938,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="78"/>
+      <c r="F24" s="83">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>15</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>9</v>
+      </c>
+      <c r="M24" s="14">
+        <v>366</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>16</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -33073,17 +33136,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>3</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>93</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>16</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -33101,17 +33176,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>12</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>9</v>
+      </c>
+      <c r="M32" s="28">
+        <v>273</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -33251,18 +33338,36 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
+      <c r="F36" s="42">
+        <v>293</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
       <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>3</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>1</v>
+      </c>
+      <c r="P36" s="42">
+        <v>13</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>4</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -33409,18 +33514,36 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
+      <c r="F42" s="42">
+        <v>293</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
       <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>3</v>
+      </c>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="42">
+        <v>13</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>4</v>
+      </c>
       <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
@@ -33462,7 +33585,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="96"/>
+      <c r="C44" s="96">
+        <f>11+12+9+273</f>
+        <v>305</v>
+      </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96"/>
     </row>
@@ -33832,12 +33958,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>109</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -33849,12 +33981,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>6</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -34020,12 +34160,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>108</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -34037,23 +34183,37 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>4</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>107</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -34065,12 +34225,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>2</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -34434,23 +34602,37 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>109</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>3</v>
+      </c>
+      <c r="L24" s="14">
+        <v>16</v>
+      </c>
+      <c r="M24" s="14">
+        <v>409</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -34620,23 +34802,37 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>3</v>
+      </c>
+      <c r="L31" s="23">
+        <v>10</v>
+      </c>
+      <c r="M31" s="23">
+        <v>129</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>100</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>1</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -34648,23 +34844,37 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>108</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>6</v>
+      </c>
+      <c r="M32" s="28">
+        <v>280</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>0</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -34795,21 +35005,49 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="42">
+        <v>20</v>
+      </c>
+      <c r="F36" s="42">
+        <v>224</v>
+      </c>
+      <c r="G36" s="42">
+        <v>7</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="I36" s="42">
+        <v>4</v>
+      </c>
+      <c r="J36" s="42">
+        <v>2</v>
+      </c>
+      <c r="K36" s="42">
+        <v>1</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>1</v>
+      </c>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
+      <c r="P36" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>3</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -34953,21 +35191,49 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
+      <c r="E42" s="42">
+        <v>20</v>
+      </c>
+      <c r="F42" s="42">
+        <v>224</v>
+      </c>
+      <c r="G42" s="42">
+        <v>7</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="I42" s="42">
+        <v>4</v>
+      </c>
+      <c r="J42" s="42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="42">
+        <v>1</v>
+      </c>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>1</v>
+      </c>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
+      <c r="P42" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>3</v>
+      </c>
       <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
@@ -35009,7 +35275,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="96"/>
+      <c r="C44" s="96">
+        <f>7+2+2+108+6+280</f>
+        <v>405</v>
+      </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96"/>
     </row>
@@ -35017,7 +35286,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="96"/>
+      <c r="C45" s="96">
+        <v>1</v>
+      </c>
       <c r="D45" s="96"/>
       <c r="E45" s="96"/>
     </row>
